--- a/data/trans_orig/P24E-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P24E-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2007</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2007 (tasa de respuesta: 98,28%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27722</t>
+          <t>28051</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46599</t>
+          <t>49171</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16842</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31638</t>
+          <t>31572</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49706</t>
+          <t>49138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73614</t>
+          <t>72571</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>41,75%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46119</t>
+          <t>45859</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67729</t>
+          <t>66552</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19625</t>
+          <t>19908</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34377</t>
+          <t>34623</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70397</t>
+          <t>71882</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96352</t>
+          <t>96335</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17344</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>34384</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9608</t>
+          <t>10480</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20998</t>
+          <t>20458</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39660</t>
+          <t>39338</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>59291</t>
+          <t>57910</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88705</t>
+          <t>87962</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47989</t>
+          <t>47200</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74058</t>
+          <t>72482</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115082</t>
+          <t>115048</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153399</t>
+          <t>154999</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>108572</t>
+          <t>109414</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>138342</t>
+          <t>138984</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>84121</t>
+          <t>86186</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>112672</t>
+          <t>113517</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>200264</t>
+          <t>201301</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>242484</t>
+          <t>242954</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>19042</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39449</t>
+          <t>39113</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>21164</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40230</t>
+          <t>42353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43638</t>
+          <t>44859</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72974</t>
+          <t>73834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16033</t>
+          <t>15569</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31914</t>
+          <t>31212</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17919</t>
+          <t>18524</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32547</t>
+          <t>32653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38548</t>
+          <t>38506</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59834</t>
+          <t>60260</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,44%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29336</t>
+          <t>29163</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45358</t>
+          <t>45994</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10913</t>
+          <t>11028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24422</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43915</t>
+          <t>44228</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66165</t>
+          <t>66388</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,67%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16512</t>
+          <t>17272</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22427</t>
+          <t>21084</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115310</t>
+          <t>115202</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>155553</t>
+          <t>154693</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>94344</t>
+          <t>91047</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>128178</t>
+          <t>125251</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>219819</t>
+          <t>220511</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>271533</t>
+          <t>268912</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>197991</t>
+          <t>196442</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>238429</t>
+          <t>237532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>124717</t>
+          <t>126402</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159573</t>
+          <t>160390</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>332451</t>
+          <t>334467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>388284</t>
+          <t>386100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>54,74%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43792</t>
+          <t>44367</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72190</t>
+          <t>70966</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>32053</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57785</t>
+          <t>57336</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>82775</t>
+          <t>85426</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>122082</t>
+          <t>122191</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2012</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2012 (tasa de respuesta: 98,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46634</t>
+          <t>47458</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70682</t>
+          <t>71844</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>34586</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56095</t>
+          <t>54940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87386</t>
+          <t>88887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120834</t>
+          <t>121748</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,49%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57803</t>
+          <t>58078</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83211</t>
+          <t>83008</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33145</t>
+          <t>33819</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53562</t>
+          <t>54140</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>98292</t>
+          <t>96853</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131570</t>
+          <t>129410</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>13653</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32096</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19118</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22732</t>
+          <t>22560</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46522</t>
+          <t>45598</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>130997</t>
+          <t>132015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>170386</t>
+          <t>171627</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>130475</t>
+          <t>131441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>167797</t>
+          <t>167077</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>271605</t>
+          <t>269591</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>326802</t>
+          <t>326285</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>169799</t>
+          <t>168731</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>210847</t>
+          <t>210596</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>107231</t>
+          <t>107872</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>143910</t>
+          <t>143468</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>288967</t>
+          <t>288636</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>345531</t>
+          <t>346785</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>49,07%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37407</t>
+          <t>37618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66517</t>
+          <t>67733</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28057</t>
+          <t>29068</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53038</t>
+          <t>54862</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73582</t>
+          <t>71961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111446</t>
+          <t>109708</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21078</t>
+          <t>20563</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>38669</t>
+          <t>39691</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20043</t>
+          <t>19855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36957</t>
+          <t>37086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44999</t>
+          <t>45718</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>70537</t>
+          <t>71517</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,81%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27299</t>
+          <t>26851</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46300</t>
+          <t>46154</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25103</t>
+          <t>24409</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42768</t>
+          <t>42381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58256</t>
+          <t>56184</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83659</t>
+          <t>82667</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,26%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17405</t>
+          <t>16917</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>6623</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20729</t>
+          <t>21736</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>12711</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32802</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>215997</t>
+          <t>215375</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>265115</t>
+          <t>264965</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>201680</t>
+          <t>200851</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>246549</t>
+          <t>246045</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>427284</t>
+          <t>432008</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>494758</t>
+          <t>496729</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,59%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>271071</t>
+          <t>270620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>322213</t>
+          <t>323323</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>180332</t>
+          <t>180426</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>224289</t>
+          <t>226940</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>467001</t>
+          <t>464173</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>535850</t>
+          <t>530033</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,87%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>64215</t>
+          <t>63366</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100432</t>
+          <t>99622</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49757</t>
+          <t>49942</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81177</t>
+          <t>81211</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>122917</t>
+          <t>123017</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>173411</t>
+          <t>172967</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2016</t>
+          <t>Población según el tiempo que hace desde que intentó por última vez dejar de fumar en 2016 (tasa de respuesta: 98,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26063</t>
+          <t>25966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9059</t>
+          <t>8785</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22957</t>
+          <t>22205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22094</t>
+          <t>21847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42193</t>
+          <t>42225</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,89%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47473</t>
+          <t>48216</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66338</t>
+          <t>66945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24373</t>
+          <t>24767</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39919</t>
+          <t>39955</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76443</t>
+          <t>77592</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101411</t>
+          <t>101836</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,27%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10681</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25974</t>
+          <t>26202</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6522</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19994</t>
+          <t>19810</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21231</t>
+          <t>20831</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41621</t>
+          <t>41268</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,26%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78544</t>
+          <t>78023</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>112870</t>
+          <t>112183</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81507</t>
+          <t>82642</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>114827</t>
+          <t>114778</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168801</t>
+          <t>169362</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>217555</t>
+          <t>216497</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,53%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>160647</t>
+          <t>160488</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>196677</t>
+          <t>197132</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128127</t>
+          <t>128656</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>163454</t>
+          <t>161772</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>293096</t>
+          <t>299192</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>347685</t>
+          <t>350787</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,95%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52112</t>
+          <t>51528</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81845</t>
+          <t>82905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32382</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57747</t>
+          <t>57097</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92571</t>
+          <t>91451</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133129</t>
+          <t>132336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27832</t>
+          <t>27166</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6275</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>18522</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20944</t>
+          <t>21495</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40784</t>
+          <t>41348</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,73%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25685</t>
+          <t>25151</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42848</t>
+          <t>42870</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22088</t>
+          <t>21798</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36110</t>
+          <t>35839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51954</t>
+          <t>52505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74000</t>
+          <t>74013</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18783</t>
+          <t>18925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>15225</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>11426</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28905</t>
+          <t>28559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110060</t>
+          <t>110866</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>152172</t>
+          <t>151163</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105432</t>
+          <t>106415</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142496</t>
+          <t>144879</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>227460</t>
+          <t>226584</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>283368</t>
+          <t>280232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>247621</t>
+          <t>246697</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>293060</t>
+          <t>292347</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186299</t>
+          <t>185159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>225398</t>
+          <t>225808</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>445245</t>
+          <t>447575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>505860</t>
+          <t>507790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,0%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77695</t>
+          <t>78966</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114016</t>
+          <t>112696</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51973</t>
+          <t>50401</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81825</t>
+          <t>80855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>136514</t>
+          <t>137531</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>182675</t>
+          <t>185416</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24E-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P24E-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28051</t>
+          <t>26394</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49171</t>
+          <t>47575</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31572</t>
+          <t>31685</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49138</t>
+          <t>48669</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72571</t>
+          <t>72388</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45859</t>
+          <t>46225</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66552</t>
+          <t>68809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,77%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19908</t>
+          <t>19784</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34623</t>
+          <t>33686</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71882</t>
+          <t>70580</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96335</t>
+          <t>97007</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17384</t>
+          <t>17270</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34384</t>
+          <t>34678</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10480</t>
+          <t>9597</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20458</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39338</t>
+          <t>40195</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,13%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57910</t>
+          <t>59346</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87962</t>
+          <t>88561</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47200</t>
+          <t>48297</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72482</t>
+          <t>74102</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115048</t>
+          <t>112726</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>154999</t>
+          <t>153693</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>109414</t>
+          <t>107817</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>138984</t>
+          <t>138594</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86186</t>
+          <t>85668</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>113517</t>
+          <t>112931</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>201301</t>
+          <t>202993</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>242954</t>
+          <t>244316</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,96%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19042</t>
+          <t>19370</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39113</t>
+          <t>39519</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21164</t>
+          <t>20323</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42353</t>
+          <t>40024</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44859</t>
+          <t>42736</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73834</t>
+          <t>71902</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15569</t>
+          <t>16048</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31212</t>
+          <t>32610</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18524</t>
+          <t>19332</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32653</t>
+          <t>33379</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>38506</t>
+          <t>37599</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60260</t>
+          <t>60058</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,26%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29163</t>
+          <t>28865</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45994</t>
+          <t>45410</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11028</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23727</t>
+          <t>23425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44228</t>
+          <t>43613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66388</t>
+          <t>65617</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,01%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>16908</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21084</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115202</t>
+          <t>115170</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>154693</t>
+          <t>152688</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>91047</t>
+          <t>93203</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125251</t>
+          <t>125986</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>220511</t>
+          <t>217737</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>268912</t>
+          <t>269655</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196442</t>
+          <t>196836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>237532</t>
+          <t>238911</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>126402</t>
+          <t>126131</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160390</t>
+          <t>160085</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>334467</t>
+          <t>333651</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>386100</t>
+          <t>385319</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44367</t>
+          <t>43852</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>70966</t>
+          <t>70992</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32053</t>
+          <t>32582</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>57336</t>
+          <t>56523</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>85426</t>
+          <t>83295</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>122191</t>
+          <t>119417</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47458</t>
+          <t>48382</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71844</t>
+          <t>71714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34586</t>
+          <t>35357</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54940</t>
+          <t>55988</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88887</t>
+          <t>87771</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121748</t>
+          <t>121161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,25%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58078</t>
+          <t>58142</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83008</t>
+          <t>82681</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33819</t>
+          <t>34167</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54140</t>
+          <t>54284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>96853</t>
+          <t>97495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>129410</t>
+          <t>129797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,69%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13653</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33040</t>
+          <t>32209</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5861</t>
+          <t>5895</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19087</t>
+          <t>18992</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22560</t>
+          <t>23185</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45598</t>
+          <t>45028</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>132015</t>
+          <t>131028</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171627</t>
+          <t>172699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>131441</t>
+          <t>131015</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>167077</t>
+          <t>167473</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,13%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>269591</t>
+          <t>273179</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>326285</t>
+          <t>329230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,59%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>168731</t>
+          <t>171207</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>210596</t>
+          <t>212938</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>107872</t>
+          <t>106529</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>143468</t>
+          <t>141715</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>288636</t>
+          <t>288271</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>346785</t>
+          <t>345131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>48,84%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37618</t>
+          <t>38489</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>67733</t>
+          <t>66212</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29068</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54862</t>
+          <t>53917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71961</t>
+          <t>74231</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109708</t>
+          <t>112380</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20563</t>
+          <t>21795</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39691</t>
+          <t>39698</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t>18543</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37086</t>
+          <t>36098</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45914</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>71517</t>
+          <t>71429</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26851</t>
+          <t>27766</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46154</t>
+          <t>45649</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24409</t>
+          <t>25618</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42381</t>
+          <t>43292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>34,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56184</t>
+          <t>57178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82667</t>
+          <t>83181</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16917</t>
+          <t>17766</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6623</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21736</t>
+          <t>20553</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12711</t>
+          <t>13580</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31800</t>
+          <t>33053</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>215375</t>
+          <t>214689</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>264965</t>
+          <t>266975</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>200851</t>
+          <t>200931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>246045</t>
+          <t>247267</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>432008</t>
+          <t>426443</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>496729</t>
+          <t>497854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>270620</t>
+          <t>269859</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>323323</t>
+          <t>324572</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>180426</t>
+          <t>178526</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>226940</t>
+          <t>225084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>464173</t>
+          <t>464846</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>530033</t>
+          <t>531589</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>48,01%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63366</t>
+          <t>64574</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>99622</t>
+          <t>101679</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49942</t>
+          <t>50001</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>81211</t>
+          <t>81714</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>123017</t>
+          <t>123947</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>172967</t>
+          <t>171579</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25966</t>
+          <t>25558</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8785</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22205</t>
+          <t>22396</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21847</t>
+          <t>21284</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42225</t>
+          <t>42226</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48216</t>
+          <t>46140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66945</t>
+          <t>66808</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24767</t>
+          <t>23909</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39955</t>
+          <t>39747</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77592</t>
+          <t>77729</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101836</t>
+          <t>102685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26202</t>
+          <t>26697</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19810</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20831</t>
+          <t>21119</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41268</t>
+          <t>41904</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78023</t>
+          <t>77923</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>112183</t>
+          <t>112872</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82642</t>
+          <t>82808</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>114778</t>
+          <t>113494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>169362</t>
+          <t>169822</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>216497</t>
+          <t>217777</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,74%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>160488</t>
+          <t>158958</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>197132</t>
+          <t>197639</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>128656</t>
+          <t>129447</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>161772</t>
+          <t>161593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>299192</t>
+          <t>297173</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>350787</t>
+          <t>347959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,5%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51528</t>
+          <t>52889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82905</t>
+          <t>82456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32619</t>
+          <t>32669</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57097</t>
+          <t>57644</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>91451</t>
+          <t>92732</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132336</t>
+          <t>132030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11855</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>28134</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>5977</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18522</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21495</t>
+          <t>20310</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41348</t>
+          <t>39302</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25151</t>
+          <t>24717</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42870</t>
+          <t>42491</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21798</t>
+          <t>22152</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35839</t>
+          <t>36171</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52505</t>
+          <t>53608</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74013</t>
+          <t>74537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,22%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>18520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4078</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15225</t>
+          <t>14851</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28559</t>
+          <t>29135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110866</t>
+          <t>109826</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>151163</t>
+          <t>152425</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>106415</t>
+          <t>105736</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144879</t>
+          <t>145061</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>226584</t>
+          <t>228083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>280232</t>
+          <t>283823</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>246697</t>
+          <t>246328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>292347</t>
+          <t>295606</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>185159</t>
+          <t>186648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>225808</t>
+          <t>228361</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>447575</t>
+          <t>444265</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>507790</t>
+          <t>507001</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,91%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78966</t>
+          <t>77092</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>112696</t>
+          <t>113847</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>50401</t>
+          <t>51691</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>80855</t>
+          <t>81297</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>137531</t>
+          <t>135435</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>185416</t>
+          <t>185190</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
